--- a/artfynd/A 37143-2026 artfynd.xlsx
+++ b/artfynd/A 37143-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,42 +797,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124638111</v>
+        <v>137286832</v>
       </c>
       <c r="B3" t="n">
-        <v>97733</v>
+        <v>97631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465682</v>
+        <v>465750</v>
       </c>
       <c r="R3" t="n">
-        <v>6331686</v>
+        <v>6331836</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,12 +874,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +894,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>ravin</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -905,13 +905,253 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Darell, Martin Andersson</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137286832</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124638111</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97733</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flishult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>465682</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6331686</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>ravin</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Darell, Martin Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/124638111</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137286792</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96619</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flishult, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>465779</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6331851</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>barrskog, brant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137286792</t>
         </is>
       </c>
     </row>
@@ -919,6 +1159,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37143-2026 artfynd.xlsx
+++ b/artfynd/A 37143-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137286832</v>
       </c>
       <c r="B3" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137286792</v>
       </c>
       <c r="B5" t="n">
-        <v>96619</v>
+        <v>96629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37143-2026 artfynd.xlsx
+++ b/artfynd/A 37143-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137286832</v>
       </c>
       <c r="B3" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137286792</v>
       </c>
       <c r="B5" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37143-2026 artfynd.xlsx
+++ b/artfynd/A 37143-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137286832</v>
       </c>
       <c r="B3" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137286792</v>
       </c>
       <c r="B5" t="n">
-        <v>96630</v>
+        <v>96635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37143-2026 artfynd.xlsx
+++ b/artfynd/A 37143-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137286832</v>
       </c>
       <c r="B3" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137286792</v>
       </c>
       <c r="B5" t="n">
-        <v>96635</v>
+        <v>96637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37143-2026 artfynd.xlsx
+++ b/artfynd/A 37143-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137286832</v>
       </c>
       <c r="B3" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137286792</v>
       </c>
       <c r="B5" t="n">
-        <v>96637</v>
+        <v>96643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37143-2026 artfynd.xlsx
+++ b/artfynd/A 37143-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137286832</v>
       </c>
       <c r="B3" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137286792</v>
       </c>
       <c r="B5" t="n">
-        <v>96643</v>
+        <v>96655</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37143-2026 artfynd.xlsx
+++ b/artfynd/A 37143-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137286832</v>
       </c>
       <c r="B3" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137286792</v>
       </c>
       <c r="B5" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37143-2026 artfynd.xlsx
+++ b/artfynd/A 37143-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137286832</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137286792</v>
       </c>
       <c r="B5" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37143-2026 artfynd.xlsx
+++ b/artfynd/A 37143-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137286832</v>
       </c>
       <c r="B3" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137286792</v>
       </c>
       <c r="B5" t="n">
-        <v>96659</v>
+        <v>96663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
